--- a/app/2025 - 2026 834 db records.xlsx
+++ b/app/2025 - 2026 834 db records.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SelmaKazanci\Downloads\project\professional 2025 reports and console logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9D17A2-E8FB-4803-B2A8-96712BB129F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0C8BF8-A8FC-4585-91D6-24EFD02A0EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="2940" windowWidth="14400" windowHeight="7270" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025_coverage_Year" sheetId="1" r:id="rId1"/>
     <sheet name="2026_coverage_Year" sheetId="2" r:id="rId2"/>
+    <sheet name="Annual Distinct counts" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="20">
   <si>
     <t>HIOS Issuer ID</t>
   </si>
@@ -77,6 +78,15 @@
   </si>
   <si>
     <t>Health</t>
+  </si>
+  <si>
+    <t>Our Enrollments Total</t>
+  </si>
+  <si>
+    <t>Our Enrollees Total</t>
+  </si>
+  <si>
+    <t>Our Raw rows</t>
   </si>
 </sst>
 </file>
@@ -2307,4 +2317,802 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF12B4B-2C79-439A-8679-2C19EB5D7A91}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>13535</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>2025</v>
+      </c>
+      <c r="D2">
+        <v>1643</v>
+      </c>
+      <c r="E2">
+        <v>2055</v>
+      </c>
+      <c r="F2">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>13535</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>2026</v>
+      </c>
+      <c r="D3">
+        <v>1861</v>
+      </c>
+      <c r="E3">
+        <v>2259</v>
+      </c>
+      <c r="F3">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>15105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>2025</v>
+      </c>
+      <c r="D4">
+        <v>42756</v>
+      </c>
+      <c r="E4">
+        <v>39181</v>
+      </c>
+      <c r="F4">
+        <v>58747</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>15105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>2026</v>
+      </c>
+      <c r="D5">
+        <v>11478</v>
+      </c>
+      <c r="E5">
+        <v>11805</v>
+      </c>
+      <c r="F5">
+        <v>13404</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>37001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>2025</v>
+      </c>
+      <c r="D6">
+        <v>11571</v>
+      </c>
+      <c r="E6">
+        <v>11809</v>
+      </c>
+      <c r="F6">
+        <v>21668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>37001</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2026</v>
+      </c>
+      <c r="D7">
+        <v>3628</v>
+      </c>
+      <c r="E7">
+        <v>4398</v>
+      </c>
+      <c r="F7">
+        <v>5423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>37301</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2025</v>
+      </c>
+      <c r="D8">
+        <v>3500</v>
+      </c>
+      <c r="E8">
+        <v>3252</v>
+      </c>
+      <c r="F8">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>37301</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>2026</v>
+      </c>
+      <c r="D9">
+        <v>1452</v>
+      </c>
+      <c r="E9">
+        <v>1453</v>
+      </c>
+      <c r="F9">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>43802</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>2025</v>
+      </c>
+      <c r="D10">
+        <v>11546</v>
+      </c>
+      <c r="E10">
+        <v>15212</v>
+      </c>
+      <c r="F10">
+        <v>18114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>43802</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>2026</v>
+      </c>
+      <c r="D11">
+        <v>17244</v>
+      </c>
+      <c r="E11">
+        <v>20972</v>
+      </c>
+      <c r="F11">
+        <v>25302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>43802</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>2025</v>
+      </c>
+      <c r="D12">
+        <v>5371</v>
+      </c>
+      <c r="E12">
+        <v>4705</v>
+      </c>
+      <c r="F12">
+        <v>5636</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>43802</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>2026</v>
+      </c>
+      <c r="D13">
+        <v>1667</v>
+      </c>
+      <c r="E13">
+        <v>1645</v>
+      </c>
+      <c r="F13">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>45334</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>2025</v>
+      </c>
+      <c r="D14">
+        <v>184900</v>
+      </c>
+      <c r="E14">
+        <v>157918</v>
+      </c>
+      <c r="F14">
+        <v>226517</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>45334</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>2026</v>
+      </c>
+      <c r="D15">
+        <v>74489</v>
+      </c>
+      <c r="E15">
+        <v>78063</v>
+      </c>
+      <c r="F15">
+        <v>87884</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>49046</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>2025</v>
+      </c>
+      <c r="D16">
+        <v>46192</v>
+      </c>
+      <c r="E16">
+        <v>49366</v>
+      </c>
+      <c r="F16">
+        <v>67690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>49046</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>2026</v>
+      </c>
+      <c r="D17">
+        <v>16870</v>
+      </c>
+      <c r="E17">
+        <v>18972</v>
+      </c>
+      <c r="F17">
+        <v>23808</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>49046</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>2025</v>
+      </c>
+      <c r="D18">
+        <v>99789</v>
+      </c>
+      <c r="E18">
+        <v>105697</v>
+      </c>
+      <c r="F18">
+        <v>142688</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>49046</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>2026</v>
+      </c>
+      <c r="D19">
+        <v>37179</v>
+      </c>
+      <c r="E19">
+        <v>41559</v>
+      </c>
+      <c r="F19">
+        <v>46784</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>58081</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>2025</v>
+      </c>
+      <c r="D20">
+        <v>302569</v>
+      </c>
+      <c r="E20">
+        <v>314694</v>
+      </c>
+      <c r="F20">
+        <v>440260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>58081</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>2026</v>
+      </c>
+      <c r="D21">
+        <v>132796</v>
+      </c>
+      <c r="E21">
+        <v>142588</v>
+      </c>
+      <c r="F21">
+        <v>169666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>60224</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <v>2025</v>
+      </c>
+      <c r="D22">
+        <v>12716</v>
+      </c>
+      <c r="E22">
+        <v>11490</v>
+      </c>
+      <c r="F22">
+        <v>59062</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>60224</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23">
+        <v>2026</v>
+      </c>
+      <c r="D23">
+        <v>19592</v>
+      </c>
+      <c r="E23">
+        <v>18855</v>
+      </c>
+      <c r="F23">
+        <v>50765</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>64357</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24">
+        <v>2025</v>
+      </c>
+      <c r="D24">
+        <v>1274</v>
+      </c>
+      <c r="E24">
+        <v>1611</v>
+      </c>
+      <c r="F24">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>64357</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <v>2026</v>
+      </c>
+      <c r="D25">
+        <v>701</v>
+      </c>
+      <c r="E25">
+        <v>967</v>
+      </c>
+      <c r="F25">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>68806</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26">
+        <v>2025</v>
+      </c>
+      <c r="D26">
+        <v>4792</v>
+      </c>
+      <c r="E26">
+        <v>8602</v>
+      </c>
+      <c r="F26">
+        <v>11358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>68806</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>2026</v>
+      </c>
+      <c r="D27">
+        <v>5402</v>
+      </c>
+      <c r="E27">
+        <v>9011</v>
+      </c>
+      <c r="F27">
+        <v>16397</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>70893</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28">
+        <v>2025</v>
+      </c>
+      <c r="D28">
+        <v>583883</v>
+      </c>
+      <c r="E28">
+        <v>544207</v>
+      </c>
+      <c r="F28">
+        <v>771880</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>70893</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29">
+        <v>2026</v>
+      </c>
+      <c r="D29">
+        <v>338423</v>
+      </c>
+      <c r="E29">
+        <v>325879</v>
+      </c>
+      <c r="F29">
+        <v>370809</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>82824</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30">
+        <v>2025</v>
+      </c>
+      <c r="D30">
+        <v>52665</v>
+      </c>
+      <c r="E30">
+        <v>60047</v>
+      </c>
+      <c r="F30">
+        <v>75315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>82824</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <v>2026</v>
+      </c>
+      <c r="D31">
+        <v>4016</v>
+      </c>
+      <c r="E31">
+        <v>5060</v>
+      </c>
+      <c r="F31">
+        <v>5936</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>83502</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>2025</v>
+      </c>
+      <c r="D32">
+        <v>2114</v>
+      </c>
+      <c r="E32">
+        <v>2416</v>
+      </c>
+      <c r="F32">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>83502</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>2026</v>
+      </c>
+      <c r="D33">
+        <v>752</v>
+      </c>
+      <c r="E33">
+        <v>824</v>
+      </c>
+      <c r="F33">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>83761</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34">
+        <v>2025</v>
+      </c>
+      <c r="D34">
+        <v>45247</v>
+      </c>
+      <c r="E34">
+        <v>41936</v>
+      </c>
+      <c r="F34">
+        <v>59023</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>83761</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35">
+        <v>2026</v>
+      </c>
+      <c r="D35">
+        <v>47735</v>
+      </c>
+      <c r="E35">
+        <v>44922</v>
+      </c>
+      <c r="F35">
+        <v>50850</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>86637</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36">
+        <v>2025</v>
+      </c>
+      <c r="D36">
+        <v>13911</v>
+      </c>
+      <c r="E36">
+        <v>16287</v>
+      </c>
+      <c r="F36">
+        <v>20652</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>86637</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>2026</v>
+      </c>
+      <c r="D37">
+        <v>4987</v>
+      </c>
+      <c r="E37">
+        <v>5860</v>
+      </c>
+      <c r="F37">
+        <v>6499</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>89942</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38">
+        <v>2025</v>
+      </c>
+      <c r="D38">
+        <v>100349</v>
+      </c>
+      <c r="E38">
+        <v>129687</v>
+      </c>
+      <c r="F38">
+        <v>150932</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>89942</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39">
+        <v>2026</v>
+      </c>
+      <c r="D39">
+        <v>104717</v>
+      </c>
+      <c r="E39">
+        <v>118249</v>
+      </c>
+      <c r="F39">
+        <v>148193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>